--- a/artfynd/A 18570-2023 artfynd.xlsx
+++ b/artfynd/A 18570-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18570-2023 artfynd.xlsx
+++ b/artfynd/A 18570-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89603552</v>
+        <v>89603518</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451369.0141679897</v>
+        <v>450964</v>
       </c>
       <c r="R2" t="n">
-        <v>7086516.07852463</v>
+        <v>7087245</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89603542</v>
+        <v>89603499</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450900.8185525986</v>
+        <v>451169</v>
       </c>
       <c r="R3" t="n">
-        <v>7087114.800719776</v>
+        <v>7086620</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,21 +844,11 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,6 +857,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Sälglåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -907,50 +882,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89603512</v>
+        <v>111936894</v>
       </c>
       <c r="B4" t="n">
-        <v>90339</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4787</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>S Lill-Veksjön Lill-Bakvattnet-Tretjärnarna norr, Jmt</t>
+          <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451408.8294837867</v>
+        <v>451168</v>
       </c>
       <c r="R4" t="n">
-        <v>7086581.080623054</v>
+        <v>7086617</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,22 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,53 +967,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89603515</v>
+        <v>89603504</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451146.0013026457</v>
+        <v>451010</v>
       </c>
       <c r="R5" t="n">
-        <v>7086637.137391253</v>
+        <v>7087255</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,21 +1047,11 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1119,11 +1060,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Rönn</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1144,37 +1080,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89603549</v>
+        <v>89603514</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1115,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451093.2089068883</v>
+        <v>451369</v>
       </c>
       <c r="R6" t="n">
-        <v>7086899.103946794</v>
+        <v>7086516</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,19 +1148,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89603522</v>
+        <v>89603519</v>
       </c>
       <c r="B7" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1192,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1216,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451176.1322889869</v>
+        <v>451093</v>
       </c>
       <c r="R7" t="n">
-        <v>7086618.170821548</v>
+        <v>7086899</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,21 +1249,11 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1356,11 +1262,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Sälgtorrträd</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1381,15 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89603545</v>
+        <v>89603522</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1421,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451261.1810146844</v>
+        <v>451176</v>
       </c>
       <c r="R8" t="n">
-        <v>7086925.988106868</v>
+        <v>7086618</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,21 +1350,11 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1477,6 +1363,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Sälgtorrträd</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1497,37 +1388,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89603529</v>
+        <v>89603550</v>
       </c>
       <c r="B9" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1537,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451155.1713344341</v>
+        <v>451145</v>
       </c>
       <c r="R9" t="n">
-        <v>7086603.08386651</v>
+        <v>7086668</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,19 +1456,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,50 +1494,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89603528</v>
+        <v>111936789</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>S Lill-Veksjön Lill-Bakvattnet-Tretjärnarna norr, Jmt</t>
+          <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451390.1352527845</v>
+        <v>450955</v>
       </c>
       <c r="R10" t="n">
-        <v>7086513.108096063</v>
+        <v>7087064</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,27 +1559,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,53 +1579,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89603514</v>
+        <v>89603512</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>4787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1779,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451369.0141679897</v>
+        <v>451409</v>
       </c>
       <c r="R11" t="n">
-        <v>7086516.07852463</v>
+        <v>7086581</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,19 +1659,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,37 +1692,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89603551</v>
+        <v>89603549</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1895,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451145.8729718246</v>
+        <v>451093</v>
       </c>
       <c r="R12" t="n">
-        <v>7086741.951211437</v>
+        <v>7086899</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1928,19 +1760,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,37 +1793,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89603550</v>
+        <v>89603551</v>
       </c>
       <c r="B13" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2011,10 +1828,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451145.1596368738</v>
+        <v>451146</v>
       </c>
       <c r="R13" t="n">
-        <v>7086667.977892813</v>
+        <v>7086742</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2044,21 +1861,11 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2067,11 +1874,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2092,50 +1894,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89603500</v>
+        <v>111936892</v>
       </c>
       <c r="B14" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>S Lill-Veksjön Lill-Bakvattnet-Tretjärnarna norr, Jmt</t>
+          <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451137.0890028827</v>
+        <v>451172</v>
       </c>
       <c r="R14" t="n">
-        <v>7086602.925613574</v>
+        <v>7086726</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2162,22 +1959,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,62 +1975,48 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Rönntorrträd</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89603499</v>
+        <v>89603530</v>
       </c>
       <c r="B15" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>6439</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2253,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451169.105952016</v>
+        <v>451065</v>
       </c>
       <c r="R15" t="n">
-        <v>7086620.041979347</v>
+        <v>7087230</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2286,21 +2059,11 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2309,11 +2072,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Sälglåga</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2334,37 +2092,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89603504</v>
+        <v>89603498</v>
       </c>
       <c r="B16" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2374,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451010.1497192787</v>
+        <v>451137</v>
       </c>
       <c r="R16" t="n">
-        <v>7087254.869899506</v>
+        <v>7086603</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2407,21 +2160,11 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2430,6 +2173,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Rönntorrträd</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2450,37 +2198,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89603548</v>
+        <v>89603501</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2490,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451150.1096876039</v>
+        <v>451189</v>
       </c>
       <c r="R17" t="n">
-        <v>7086730.875623316</v>
+        <v>7086597</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2523,26 +2266,11 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2551,6 +2279,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Sälglåga</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2571,15 +2304,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89603537</v>
+        <v>89603509</v>
       </c>
       <c r="B18" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2611,10 +2339,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451176.1322889869</v>
+        <v>451155</v>
       </c>
       <c r="R18" t="n">
-        <v>7086618.170821548</v>
+        <v>7086603</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2644,21 +2372,11 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2670,7 +2388,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Sälgtorrträd</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2692,37 +2410,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89603518</v>
+        <v>89603515</v>
       </c>
       <c r="B19" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2732,10 +2445,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450964.1438083696</v>
+        <v>451146</v>
       </c>
       <c r="R19" t="n">
-        <v>7087245.022874629</v>
+        <v>7086637</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,21 +2478,11 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2788,6 +2491,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Rönn</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2808,37 +2516,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89603541</v>
+        <v>89603537</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2848,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451393.7852954725</v>
+        <v>451176</v>
       </c>
       <c r="R20" t="n">
-        <v>7086577.790934764</v>
+        <v>7086618</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2881,26 +2584,11 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2909,6 +2597,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Sälgtorrträd</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2929,50 +2622,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89603519</v>
+        <v>111936854</v>
       </c>
       <c r="B21" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>S Lill-Veksjön Lill-Bakvattnet-Tretjärnarna norr, Jmt</t>
+          <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451093.2089068883</v>
+        <v>450998</v>
       </c>
       <c r="R21" t="n">
-        <v>7086899.103946794</v>
+        <v>7087289</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2999,22 +2687,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3029,53 +2707,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89603501</v>
+        <v>89603528</v>
       </c>
       <c r="B22" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3085,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451189.0287022752</v>
+        <v>451390</v>
       </c>
       <c r="R22" t="n">
-        <v>7086596.830682659</v>
+        <v>7086513</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3118,19 +2787,14 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3141,11 +2805,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Sälglåga</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3166,37 +2825,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>89603530</v>
+        <v>89603541</v>
       </c>
       <c r="B23" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3206,10 +2860,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451064.8678781405</v>
+        <v>451394</v>
       </c>
       <c r="R23" t="n">
-        <v>7087229.797013092</v>
+        <v>7086578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3239,19 +2893,14 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3282,37 +2931,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89603498</v>
+        <v>89603548</v>
       </c>
       <c r="B24" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3322,10 +2966,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451137.0890028827</v>
+        <v>451150</v>
       </c>
       <c r="R24" t="n">
-        <v>7086602.925613574</v>
+        <v>7086731</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3355,19 +2999,14 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3378,11 +3017,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Rönntorrträd</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3403,15 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111936864</v>
+        <v>111936793</v>
       </c>
       <c r="B25" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3419,34 +3048,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451094</v>
+        <v>451089</v>
       </c>
       <c r="R25" t="n">
-        <v>7087213</v>
+        <v>7087232</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3479,6 +3112,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3505,50 +3143,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111936894</v>
+        <v>111936794</v>
       </c>
       <c r="B26" t="n">
-        <v>90113</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451169</v>
+        <v>451105</v>
       </c>
       <c r="R26" t="n">
-        <v>7086617</v>
+        <v>7087168</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3581,6 +3218,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3607,15 +3249,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111936793</v>
+        <v>89603506</v>
       </c>
       <c r="B27" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,16 +3260,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3641,20 +3278,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>rörvattsbodarna, Jmt</t>
+          <t>S Lill-Veksjön Lill-Bakvattnet-Tretjärnarna norr, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>451089</v>
+        <v>450868</v>
       </c>
       <c r="R27" t="n">
-        <v>7087233</v>
+        <v>7087202</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3681,17 +3314,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3706,27 +3334,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111936789</v>
+        <v>89603540</v>
       </c>
       <c r="B28" t="n">
-        <v>90235</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3734,34 +3361,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>rörvattsbodarna, Jmt</t>
+          <t>S Lill-Veksjön Lill-Bakvattnet-Tretjärnarna norr, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450955</v>
+        <v>451362</v>
       </c>
       <c r="R28" t="n">
-        <v>7087064</v>
+        <v>7086480</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3788,12 +3415,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3808,62 +3435,61 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111936860</v>
+        <v>89603500</v>
       </c>
       <c r="B29" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80398</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>229748</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>rörvattsbodarna, Jmt</t>
+          <t>S Lill-Veksjön Lill-Bakvattnet-Tretjärnarna norr, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450975</v>
+        <v>451137</v>
       </c>
       <c r="R29" t="n">
-        <v>7086983</v>
+        <v>7086603</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3890,12 +3516,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3906,223 +3532,28 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Rönntorrträd</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>111936854</v>
-      </c>
-      <c r="B30" t="n">
-        <v>56446</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>rörvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>450998</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7087289</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>111936892</v>
-      </c>
-      <c r="B31" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>rörvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>451172</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7086727</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18570-2023 artfynd.xlsx
+++ b/artfynd/A 18570-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603518</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603499</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936894</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603504</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603514</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603519</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603522</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603550</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1588,6 +1633,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936789</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1689,6 +1739,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603512</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1790,6 +1845,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603549</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603551</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1988,6 +2053,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936892</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2089,6 +2159,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603530</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2195,6 +2270,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603498</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2301,6 +2381,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603501</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2407,6 +2492,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603509</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2513,6 +2603,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603515</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2619,6 +2714,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603537</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2716,6 +2816,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936854</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2822,6 +2927,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603528</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2928,6 +3038,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603541</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3032,6 +3147,11 @@
       <c r="AY24" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603548</t>
         </is>
       </c>
     </row>
@@ -3140,6 +3260,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936793</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3246,6 +3371,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936794</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3347,6 +3477,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603506</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3448,6 +3583,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603540</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3554,8 +3694,43 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603500</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>